--- a/NYKAA_CUSTOMER_LOYALTY_ANALYSIS_SOR_MODEL.xlsx
+++ b/NYKAA_CUSTOMER_LOYALTY_ANALYSIS_SOR_MODEL.xlsx
@@ -8,29 +8,30 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/17a22fede820b6e8/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{529D60E9-14BD-44FB-BB41-8A8B0112484C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="14_{D0D324B5-9185-4B7B-9AD3-B52650E18FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="4" xr2:uid="{8A33CC25-353A-4FF0-8045-B53F2FA831C0}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="5" xr2:uid="{8A33CC25-353A-4FF0-8045-B53F2FA831C0}"/>
   </bookViews>
   <sheets>
     <sheet name="RAW DATA" sheetId="1" r:id="rId1"/>
     <sheet name="NUMERICAL DATA" sheetId="2" r:id="rId2"/>
     <sheet name="AVG S-O-R" sheetId="3" r:id="rId3"/>
-    <sheet name="PIVOT BY AGE, STIMULI" sheetId="6" r:id="rId4"/>
-    <sheet name="DASHBOARD" sheetId="8" r:id="rId5"/>
+    <sheet name="PIVOT AGE" sheetId="9" r:id="rId4"/>
+    <sheet name="PIVOT STIMULI" sheetId="6" r:id="rId5"/>
+    <sheet name="DASHBOARD" sheetId="8" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="Slicer_Gender">#N/A</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="39" r:id="rId6"/>
-    <pivotCache cacheId="38" r:id="rId7"/>
+    <pivotCache cacheId="1" r:id="rId7"/>
+    <pivotCache cacheId="8" r:id="rId8"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
       <x14:slicerCaches>
-        <x14:slicerCache r:id="rId8"/>
+        <x14:slicerCache r:id="rId9"/>
       </x14:slicerCaches>
     </ext>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
@@ -869,7 +870,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -938,13 +939,252 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="6">
+  <dxfs count="86">
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="169" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="168" formatCode="0.0000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="0.00000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="0.000000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="0.0000000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.00000000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="169" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="168" formatCode="0.0000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="0.00000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="0.000000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="0.0000000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.00000000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="169" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="168" formatCode="0.0000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="0.00000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="0.000000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="0.0000000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.00000000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="169" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="168" formatCode="0.0000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="0.00000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="0.000000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="0.0000000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.00000000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="169" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="168" formatCode="0.0000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="0.00000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="0.000000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="0.0000000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.00000000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="2" formatCode="0.00"/>
     </dxf>
@@ -1359,7 +1599,495 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[NYKAA_CUSTOMER_LOYALTY_ANALYSIS_SOR_MODEL.xlsx]PIVOT BY AGE, STIMULI!PivotTable2</c:name>
+    <c:name>[NYKAA_CUSTOMER_LOYALTY_ANALYSIS_SOR_MODEL.xlsx]PIVOT AGE!PivotTable1</c:name>
+    <c:fmtId val="3"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-IN" baseline="0"/>
+              <a:t>Loyalty Score by Age Group</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-IN"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'PIVOT AGE'!$B$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'PIVOT AGE'!$A$4:$A$8</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Below 20</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>21-30</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>31-40</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Above 40</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'PIVOT AGE'!$B$4:$B$8</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>3.0181818181818185</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3.7253333333333321</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3.4545454545454546</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3.4571428571428577</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-4DB0-4679-B423-41FB426E3A05}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="580220544"/>
+        <c:axId val="580220064"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="580220544"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="580220064"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="580220064"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.00" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="580220544"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[NYKAA_CUSTOMER_LOYALTY_ANALYSIS_SOR_MODEL.xlsx]PIVOT STIMULI!PivotTable2</c:name>
     <c:fmtId val="1"/>
   </c:pivotSource>
   <c:chart>
@@ -1431,6 +2159,32 @@
       <c:pivotFmt>
         <c:idx val="0"/>
         <c:spPr>
+          <a:gradFill rotWithShape="1">
+            <a:gsLst>
+              <a:gs pos="0">
+                <a:schemeClr val="accent1">
+                  <a:satMod val="103000"/>
+                  <a:lumMod val="102000"/>
+                  <a:tint val="94000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="50000">
+                <a:schemeClr val="accent1">
+                  <a:satMod val="110000"/>
+                  <a:lumMod val="100000"/>
+                  <a:shade val="100000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="100000">
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="99000"/>
+                  <a:satMod val="120000"/>
+                  <a:shade val="78000"/>
+                </a:schemeClr>
+              </a:gs>
+            </a:gsLst>
+            <a:lin ang="5400000" scaled="0"/>
+          </a:gradFill>
           <a:ln w="34925" cap="rnd">
             <a:solidFill>
               <a:srgbClr val="FF99FF"/>
@@ -1539,6 +2293,15 @@
               <a:endParaRPr lang="en-US"/>
             </a:p>
           </c:txPr>
+          <c:showLegendKey val="1"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="1"/>
+          <c:showSerName val="1"/>
+          <c:showPercent val="1"/>
+          <c:showBubbleSize val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
         </c:dLbl>
       </c:pivotFmt>
       <c:pivotFmt>
@@ -2071,7 +2834,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'PIVOT BY AGE, STIMULI'!$B$3</c:f>
+              <c:f>'PIVOT STIMULI'!$B$3</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2140,6 +2903,168 @@
               </a:effectLst>
             </c:spPr>
           </c:marker>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:marker>
+              <c:symbol val="circle"/>
+              <c:size val="6"/>
+              <c:spPr>
+                <a:gradFill rotWithShape="1">
+                  <a:gsLst>
+                    <a:gs pos="0">
+                      <a:schemeClr val="accent1">
+                        <a:satMod val="103000"/>
+                        <a:lumMod val="102000"/>
+                        <a:tint val="94000"/>
+                      </a:schemeClr>
+                    </a:gs>
+                    <a:gs pos="50000">
+                      <a:schemeClr val="accent1">
+                        <a:satMod val="110000"/>
+                        <a:lumMod val="100000"/>
+                        <a:shade val="100000"/>
+                      </a:schemeClr>
+                    </a:gs>
+                    <a:gs pos="100000">
+                      <a:schemeClr val="accent1">
+                        <a:lumMod val="99000"/>
+                        <a:satMod val="120000"/>
+                        <a:shade val="78000"/>
+                      </a:schemeClr>
+                    </a:gs>
+                  </a:gsLst>
+                  <a:lin ang="5400000" scaled="0"/>
+                </a:gradFill>
+                <a:ln w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="FF99FF"/>
+                  </a:solidFill>
+                  <a:round/>
+                </a:ln>
+                <a:effectLst>
+                  <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+                    <a:srgbClr val="000000">
+                      <a:alpha val="63000"/>
+                    </a:srgbClr>
+                  </a:outerShdw>
+                </a:effectLst>
+              </c:spPr>
+            </c:marker>
+            <c:bubble3D val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000000-4D15-4C24-844D-96297EEE972B}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:marker>
+              <c:symbol val="circle"/>
+              <c:size val="6"/>
+              <c:spPr>
+                <a:gradFill rotWithShape="1">
+                  <a:gsLst>
+                    <a:gs pos="0">
+                      <a:schemeClr val="accent1">
+                        <a:satMod val="103000"/>
+                        <a:lumMod val="102000"/>
+                        <a:tint val="94000"/>
+                      </a:schemeClr>
+                    </a:gs>
+                    <a:gs pos="50000">
+                      <a:schemeClr val="accent1">
+                        <a:satMod val="110000"/>
+                        <a:lumMod val="100000"/>
+                        <a:shade val="100000"/>
+                      </a:schemeClr>
+                    </a:gs>
+                    <a:gs pos="100000">
+                      <a:schemeClr val="accent1">
+                        <a:lumMod val="99000"/>
+                        <a:satMod val="120000"/>
+                        <a:shade val="78000"/>
+                      </a:schemeClr>
+                    </a:gs>
+                  </a:gsLst>
+                  <a:lin ang="5400000" scaled="0"/>
+                </a:gradFill>
+                <a:ln w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="FF99FF"/>
+                  </a:solidFill>
+                  <a:round/>
+                </a:ln>
+                <a:effectLst>
+                  <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+                    <a:srgbClr val="000000">
+                      <a:alpha val="63000"/>
+                    </a:srgbClr>
+                  </a:outerShdw>
+                </a:effectLst>
+              </c:spPr>
+            </c:marker>
+            <c:bubble3D val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-4D15-4C24-844D-96297EEE972B}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:marker>
+              <c:symbol val="circle"/>
+              <c:size val="6"/>
+              <c:spPr>
+                <a:gradFill rotWithShape="1">
+                  <a:gsLst>
+                    <a:gs pos="0">
+                      <a:schemeClr val="accent1">
+                        <a:satMod val="103000"/>
+                        <a:lumMod val="102000"/>
+                        <a:tint val="94000"/>
+                      </a:schemeClr>
+                    </a:gs>
+                    <a:gs pos="50000">
+                      <a:schemeClr val="accent1">
+                        <a:satMod val="110000"/>
+                        <a:lumMod val="100000"/>
+                        <a:shade val="100000"/>
+                      </a:schemeClr>
+                    </a:gs>
+                    <a:gs pos="100000">
+                      <a:schemeClr val="accent1">
+                        <a:lumMod val="99000"/>
+                        <a:satMod val="120000"/>
+                        <a:shade val="78000"/>
+                      </a:schemeClr>
+                    </a:gs>
+                  </a:gsLst>
+                  <a:lin ang="5400000" scaled="0"/>
+                </a:gradFill>
+                <a:ln w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="FF99FF"/>
+                  </a:solidFill>
+                  <a:round/>
+                </a:ln>
+                <a:effectLst>
+                  <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+                    <a:srgbClr val="000000">
+                      <a:alpha val="63000"/>
+                    </a:srgbClr>
+                  </a:outerShdw>
+                </a:effectLst>
+              </c:spPr>
+            </c:marker>
+            <c:bubble3D val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000002-4D15-4C24-844D-96297EEE972B}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
           <c:dLbls>
             <c:dLbl>
               <c:idx val="0"/>
@@ -2157,6 +3082,9 @@
               <c:showBubbleSize val="0"/>
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000000-4D15-4C24-844D-96297EEE972B}"/>
+                </c:ext>
               </c:extLst>
             </c:dLbl>
             <c:dLbl>
@@ -2175,6 +3103,9 @@
               <c:showBubbleSize val="0"/>
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000001-4D15-4C24-844D-96297EEE972B}"/>
+                </c:ext>
               </c:extLst>
             </c:dLbl>
             <c:dLbl>
@@ -2193,6 +3124,9 @@
               <c:showBubbleSize val="0"/>
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000002-4D15-4C24-844D-96297EEE972B}"/>
+                </c:ext>
               </c:extLst>
             </c:dLbl>
             <c:spPr>
@@ -2258,7 +3192,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'PIVOT BY AGE, STIMULI'!$A$4:$A$7</c:f>
+              <c:f>'PIVOT STIMULI'!$A$4:$A$7</c:f>
               <c:strCache>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
@@ -2275,7 +3209,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'PIVOT BY AGE, STIMULI'!$B$4:$B$7</c:f>
+              <c:f>'PIVOT STIMULI'!$B$4:$B$7</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
@@ -2510,560 +3444,6 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="all" spc="120" normalizeH="0" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="en-IN"/>
-              <a:t>Loyalty score by Age Group</a:t>
-            </a:r>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="all" spc="120" normalizeH="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:pivotFmts>
-      <c:pivotFmt>
-        <c:idx val="0"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1"/>
-          </a:solidFill>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="diamond"/>
-          <c:size val="6"/>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent1"/>
-            </a:solidFill>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="50000"/>
-                      <a:lumOff val="50000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-          <c:dLblPos val="outEnd"/>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="1"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="1"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1"/>
-          </a:solidFill>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="none"/>
-        </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="50000"/>
-                      <a:lumOff val="50000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-          <c:dLblPos val="outEnd"/>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="1"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="2"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1"/>
-          </a:solidFill>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="none"/>
-        </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="50000"/>
-                      <a:lumOff val="50000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-          <c:dLblPos val="outEnd"/>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="1"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-    </c:pivotFmts>
-    <c:plotArea>
-      <c:layout/>
-      <c:barChart>
-        <c:barDir val="col"/>
-        <c:grouping val="clustered"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:v>Total</c:v>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent1"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:txPr>
-              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                <a:spAutoFit/>
-              </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="50000"/>
-                        <a:lumOff val="50000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:endParaRPr lang="en-US"/>
-              </a:p>
-            </c:txPr>
-            <c:dLblPos val="outEnd"/>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-                <c15:leaderLines>
-                  <c:spPr>
-                    <a:ln w="9525">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="35000"/>
-                          <a:lumOff val="65000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                    </a:ln>
-                    <a:effectLst/>
-                  </c:spPr>
-                </c15:leaderLines>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:cat>
-            <c:strLit>
-              <c:ptCount val="4"/>
-              <c:pt idx="0">
-                <c:v>Below 20</c:v>
-              </c:pt>
-              <c:pt idx="1">
-                <c:v>21-30</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>31-40</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>Above 40</c:v>
-              </c:pt>
-            </c:strLit>
-          </c:cat>
-          <c:val>
-            <c:numLit>
-              <c:formatCode>General</c:formatCode>
-              <c:ptCount val="4"/>
-              <c:pt idx="0">
-                <c:v>2.75</c:v>
-              </c:pt>
-              <c:pt idx="1">
-                <c:v>3.6187500000000004</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>2.8</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>3.2666666666666662</c:v>
-              </c:pt>
-            </c:numLit>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-9D93-4361-B81D-A93544758C2E}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:dLblPos val="outEnd"/>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="1"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:gapWidth val="444"/>
-        <c:overlap val="-90"/>
-        <c:axId val="1558563168"/>
-        <c:axId val="1558566528"/>
-      </c:barChart>
-      <c:catAx>
-        <c:axId val="1558563168"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="800" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="all" spc="120" normalizeH="0" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1558566528"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="1558566528"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="1"/>
-        <c:axPos val="l"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="1558563168"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:legend>
-      <c:legendPos val="r"/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:legend>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="lt1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="en-US"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-  <c:extLst/>
-</c:chartSpace>
-</file>
-
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
@@ -3077,676 +3457,8 @@
       <c:style val="2"/>
     </mc:Fallback>
   </mc:AlternateContent>
-  <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="all" spc="120" normalizeH="0" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="en-IN"/>
-              <a:t>Loyalty score by Age Group</a:t>
-            </a:r>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="all" spc="120" normalizeH="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:pivotFmts>
-      <c:pivotFmt>
-        <c:idx val="0"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1"/>
-          </a:solidFill>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="diamond"/>
-          <c:size val="6"/>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent1"/>
-            </a:solidFill>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="50000"/>
-                      <a:lumOff val="50000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-          <c:dLblPos val="outEnd"/>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="1"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="1"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1"/>
-          </a:solidFill>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="none"/>
-        </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="50000"/>
-                      <a:lumOff val="50000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-          <c:dLblPos val="outEnd"/>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="1"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="2"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1"/>
-          </a:solidFill>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="none"/>
-        </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="50000"/>
-                      <a:lumOff val="50000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-          <c:dLblPos val="outEnd"/>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="1"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="3"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1"/>
-          </a:solidFill>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="none"/>
-        </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="50000"/>
-                      <a:lumOff val="50000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-          <c:dLblPos val="outEnd"/>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="1"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="4"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1"/>
-          </a:solidFill>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="none"/>
-        </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="50000"/>
-                      <a:lumOff val="50000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-          <c:dLblPos val="outEnd"/>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="1"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-    </c:pivotFmts>
-    <c:plotArea>
-      <c:layout/>
-      <c:barChart>
-        <c:barDir val="col"/>
-        <c:grouping val="clustered"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:v>Total</c:v>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent1"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:txPr>
-              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                <a:spAutoFit/>
-              </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="50000"/>
-                        <a:lumOff val="50000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:endParaRPr lang="en-US"/>
-              </a:p>
-            </c:txPr>
-            <c:dLblPos val="outEnd"/>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-                <c15:leaderLines>
-                  <c:spPr>
-                    <a:ln w="9525">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="35000"/>
-                          <a:lumOff val="65000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                    </a:ln>
-                    <a:effectLst/>
-                  </c:spPr>
-                </c15:leaderLines>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:cat>
-            <c:strLit>
-              <c:ptCount val="4"/>
-              <c:pt idx="0">
-                <c:v>Below 20</c:v>
-              </c:pt>
-              <c:pt idx="1">
-                <c:v>21-30</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>31-40</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>Above 40</c:v>
-              </c:pt>
-            </c:strLit>
-          </c:cat>
-          <c:val>
-            <c:numLit>
-              <c:formatCode>General</c:formatCode>
-              <c:ptCount val="4"/>
-              <c:pt idx="0">
-                <c:v>2.75</c:v>
-              </c:pt>
-              <c:pt idx="1">
-                <c:v>3.6187500000000004</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>2.8</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>3.2666666666666662</c:v>
-              </c:pt>
-            </c:numLit>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-17B3-4688-81B3-9FC8677A8CE8}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:dLblPos val="outEnd"/>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="1"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:gapWidth val="444"/>
-        <c:overlap val="-90"/>
-        <c:axId val="1558563168"/>
-        <c:axId val="1558566528"/>
-      </c:barChart>
-      <c:catAx>
-        <c:axId val="1558563168"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="800" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="all" spc="120" normalizeH="0" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1558566528"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="1558566528"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="1"/>
-        <c:axPos val="l"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="1558563168"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:legend>
-      <c:legendPos val="r"/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:legend>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="lt1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="en-US"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-  <c:extLst/>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[NYKAA_CUSTOMER_LOYALTY_ANALYSIS_SOR_MODEL.xlsx]PIVOT BY AGE, STIMULI!PivotTable2</c:name>
+    <c:name>[NYKAA_CUSTOMER_LOYALTY_ANALYSIS_SOR_MODEL.xlsx]PIVOT STIMULI!PivotTable2</c:name>
     <c:fmtId val="7"/>
   </c:pivotSource>
   <c:chart>
@@ -3952,6 +3664,15 @@
               <a:endParaRPr lang="en-US"/>
             </a:p>
           </c:txPr>
+          <c:showLegendKey val="1"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="1"/>
+          <c:showSerName val="1"/>
+          <c:showPercent val="1"/>
+          <c:showBubbleSize val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
         </c:dLbl>
       </c:pivotFmt>
       <c:pivotFmt>
@@ -5911,7 +5632,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'PIVOT BY AGE, STIMULI'!$B$3</c:f>
+              <c:f>'PIVOT STIMULI'!$B$3</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -5980,6 +5701,213 @@
               </a:effectLst>
             </c:spPr>
           </c:marker>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:marker>
+              <c:symbol val="circle"/>
+              <c:size val="6"/>
+              <c:spPr>
+                <a:gradFill rotWithShape="1">
+                  <a:gsLst>
+                    <a:gs pos="0">
+                      <a:schemeClr val="accent1">
+                        <a:satMod val="103000"/>
+                        <a:lumMod val="102000"/>
+                        <a:tint val="94000"/>
+                      </a:schemeClr>
+                    </a:gs>
+                    <a:gs pos="50000">
+                      <a:schemeClr val="accent1">
+                        <a:satMod val="110000"/>
+                        <a:lumMod val="100000"/>
+                        <a:shade val="100000"/>
+                      </a:schemeClr>
+                    </a:gs>
+                    <a:gs pos="100000">
+                      <a:schemeClr val="accent1">
+                        <a:lumMod val="99000"/>
+                        <a:satMod val="120000"/>
+                        <a:shade val="78000"/>
+                      </a:schemeClr>
+                    </a:gs>
+                  </a:gsLst>
+                  <a:lin ang="5400000" scaled="0"/>
+                </a:gradFill>
+                <a:ln w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="FF99FF"/>
+                  </a:solidFill>
+                  <a:round/>
+                </a:ln>
+                <a:effectLst>
+                  <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+                    <a:srgbClr val="000000">
+                      <a:alpha val="63000"/>
+                    </a:srgbClr>
+                  </a:outerShdw>
+                </a:effectLst>
+              </c:spPr>
+            </c:marker>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:ln w="34925" cap="rnd">
+                <a:solidFill>
+                  <a:srgbClr val="FF99FF"/>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+                  <a:srgbClr val="000000">
+                    <a:alpha val="63000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000000-CF8D-45F7-A64E-6A5944F19C52}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:marker>
+              <c:symbol val="circle"/>
+              <c:size val="6"/>
+              <c:spPr>
+                <a:gradFill rotWithShape="1">
+                  <a:gsLst>
+                    <a:gs pos="0">
+                      <a:schemeClr val="accent1">
+                        <a:satMod val="103000"/>
+                        <a:lumMod val="102000"/>
+                        <a:tint val="94000"/>
+                      </a:schemeClr>
+                    </a:gs>
+                    <a:gs pos="50000">
+                      <a:schemeClr val="accent1">
+                        <a:satMod val="110000"/>
+                        <a:lumMod val="100000"/>
+                        <a:shade val="100000"/>
+                      </a:schemeClr>
+                    </a:gs>
+                    <a:gs pos="100000">
+                      <a:schemeClr val="accent1">
+                        <a:lumMod val="99000"/>
+                        <a:satMod val="120000"/>
+                        <a:shade val="78000"/>
+                      </a:schemeClr>
+                    </a:gs>
+                  </a:gsLst>
+                  <a:lin ang="5400000" scaled="0"/>
+                </a:gradFill>
+                <a:ln w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="FF99FF"/>
+                  </a:solidFill>
+                  <a:round/>
+                </a:ln>
+                <a:effectLst>
+                  <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+                    <a:srgbClr val="000000">
+                      <a:alpha val="63000"/>
+                    </a:srgbClr>
+                  </a:outerShdw>
+                </a:effectLst>
+              </c:spPr>
+            </c:marker>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:ln w="34925" cap="rnd">
+                <a:solidFill>
+                  <a:srgbClr val="FF99FF"/>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+                  <a:srgbClr val="000000">
+                    <a:alpha val="63000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-CF8D-45F7-A64E-6A5944F19C52}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:marker>
+              <c:symbol val="circle"/>
+              <c:size val="6"/>
+              <c:spPr>
+                <a:gradFill rotWithShape="1">
+                  <a:gsLst>
+                    <a:gs pos="0">
+                      <a:schemeClr val="accent1">
+                        <a:satMod val="103000"/>
+                        <a:lumMod val="102000"/>
+                        <a:tint val="94000"/>
+                      </a:schemeClr>
+                    </a:gs>
+                    <a:gs pos="50000">
+                      <a:schemeClr val="accent1">
+                        <a:satMod val="110000"/>
+                        <a:lumMod val="100000"/>
+                        <a:shade val="100000"/>
+                      </a:schemeClr>
+                    </a:gs>
+                    <a:gs pos="100000">
+                      <a:schemeClr val="accent1">
+                        <a:lumMod val="99000"/>
+                        <a:satMod val="120000"/>
+                        <a:shade val="78000"/>
+                      </a:schemeClr>
+                    </a:gs>
+                  </a:gsLst>
+                  <a:lin ang="5400000" scaled="0"/>
+                </a:gradFill>
+                <a:ln w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="FF99FF"/>
+                  </a:solidFill>
+                  <a:round/>
+                </a:ln>
+                <a:effectLst>
+                  <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+                    <a:srgbClr val="000000">
+                      <a:alpha val="63000"/>
+                    </a:srgbClr>
+                  </a:outerShdw>
+                </a:effectLst>
+              </c:spPr>
+            </c:marker>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:ln w="34925" cap="rnd">
+                <a:solidFill>
+                  <a:srgbClr val="FF99FF"/>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+                  <a:srgbClr val="000000">
+                    <a:alpha val="63000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000002-CF8D-45F7-A64E-6A5944F19C52}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
           <c:dLbls>
             <c:dLbl>
               <c:idx val="0"/>
@@ -5997,6 +5925,9 @@
               <c:showBubbleSize val="0"/>
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000000-CF8D-45F7-A64E-6A5944F19C52}"/>
+                </c:ext>
               </c:extLst>
             </c:dLbl>
             <c:dLbl>
@@ -6015,6 +5946,9 @@
               <c:showBubbleSize val="0"/>
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000001-CF8D-45F7-A64E-6A5944F19C52}"/>
+                </c:ext>
               </c:extLst>
             </c:dLbl>
             <c:dLbl>
@@ -6033,6 +5967,9 @@
               <c:showBubbleSize val="0"/>
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000002-CF8D-45F7-A64E-6A5944F19C52}"/>
+                </c:ext>
               </c:extLst>
             </c:dLbl>
             <c:spPr>
@@ -6098,7 +6035,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'PIVOT BY AGE, STIMULI'!$A$4:$A$7</c:f>
+              <c:f>'PIVOT STIMULI'!$A$4:$A$7</c:f>
               <c:strCache>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
@@ -6115,7 +6052,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'PIVOT BY AGE, STIMULI'!$B$4:$B$7</c:f>
+              <c:f>'PIVOT STIMULI'!$B$4:$B$7</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
@@ -6249,6 +6186,608 @@
           </a:p>
         </c:txPr>
         <c:crossAx val="1558560768"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[NYKAA_CUSTOMER_LOYALTY_ANALYSIS_SOR_MODEL.xlsx]PIVOT AGE!PivotTable1</c:name>
+    <c:fmtId val="5"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-IN" baseline="0"/>
+              <a:t>Loyalty Score by Age Group</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-IN"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-IN"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'PIVOT AGE'!$B$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'PIVOT AGE'!$A$4:$A$8</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Below 20</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>21-30</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>31-40</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Above 40</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'PIVOT AGE'!$B$4:$B$8</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>3.0181818181818185</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3.7253333333333321</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3.4545454545454546</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3.4571428571428577</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-AA13-4ECC-B212-5C009E5184C9}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="580220544"/>
+        <c:axId val="580220064"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="580220544"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="580220064"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="580220064"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.00" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="580220544"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7056,6 +7595,509 @@
 </file>
 
 <file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="351">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -7557,1055 +8599,7 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="202">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200" cap="all"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="800" kern="1200" cap="all" spc="120" normalizeH="0" baseline="0"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="50000"/>
-        <a:lumOff val="50000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0"/>
-    <cs:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-    </cs:spPr>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-    </cs:spPr>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="22225" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout size="6"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="75000"/>
-          <a:lumOff val="25000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1600" b="1" kern="1200" cap="all" spc="120" normalizeH="0" baseline="0"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:prstDash val="sysDash"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="800" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-  </cs:wall>
-</cs:chartStyle>
-</file>
-
 <file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="202">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200" cap="all"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="800" kern="1200" cap="all" spc="120" normalizeH="0" baseline="0"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="50000"/>
-        <a:lumOff val="50000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0"/>
-    <cs:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-    </cs:spPr>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-    </cs:spPr>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="22225" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout size="6"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="75000"/>
-          <a:lumOff val="25000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1600" b="1" kern="1200" cap="all" spc="120" normalizeH="0" baseline="0"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:prstDash val="sysDash"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="800" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-  </cs:wall>
-</cs:chartStyle>
-</file>
-
-<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="351">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -9107,6 +9101,509 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
@@ -9336,6 +9833,47 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>2270760</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>457200</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E372999E-8902-8762-A537-84B6A2D2A4F8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>411480</xdr:colOff>
       <xdr:row>4</xdr:row>
@@ -9370,48 +9908,10 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>335280</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="3" name="Chart 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{49B4E206-7F31-4C69-9279-FCCFDBB57E5D}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr>
-          <a:graphicFrameLocks/>
-        </xdr:cNvGraphicFramePr>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -10449,44 +10949,6 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>99060</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>30480</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>15240</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>53340</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="22" name="Chart 21">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2EC2541C-9005-43CF-8FA6-D5C685CBD6D0}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr>
-          <a:graphicFrameLocks/>
-        </xdr:cNvGraphicFramePr>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>22</xdr:row>
@@ -10517,6 +10979,44 @@
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>167640</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FE30BC86-8B0F-4FB9-8312-FEDB8A8CFBB6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
@@ -10525,25 +11025,25 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>403860</xdr:colOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>15240</xdr:colOff>
       <xdr:row>48</xdr:row>
-      <xdr:rowOff>137160</xdr:rowOff>
+      <xdr:rowOff>121920</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>403860</xdr:colOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>15240</xdr:colOff>
       <xdr:row>62</xdr:row>
-      <xdr:rowOff>43815</xdr:rowOff>
+      <xdr:rowOff>28575</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
-            <xdr:cNvPr id="29" name="Gender">
+            <xdr:cNvPr id="4" name="Gender">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1102EE17-ADE9-FAB5-02C8-1D38B93CF737}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4682E894-0725-DE9A-49C2-E729F82BB4EC}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -10570,7 +11070,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="3451860" y="8915400"/>
+              <a:off x="4282440" y="8900160"/>
               <a:ext cx="1828800" cy="2466975"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -10605,7 +11105,33 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Ananya Dwivedi" refreshedDate="46133.631953935183" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="105" xr:uid="{31C7BFD8-A732-4DDB-9E22-80E8892EA3DF}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Ananya Dwivedi" refreshedDate="46133.63565625" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="4" xr:uid="{A6D95273-D309-48CA-82BE-3129668C0243}">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="A3:B7" sheet="PIVOT STIMULI"/>
+  </cacheSource>
+  <cacheFields count="2">
+    <cacheField name="Row Labels" numFmtId="0">
+      <sharedItems count="4">
+        <s v="ADS"/>
+        <s v="QUALITY"/>
+        <s v="VALUE"/>
+        <s v="Grand Total"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Average of SCORE" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0.64" maxValue="0.75"/>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Ananya Dwivedi" refreshedDate="46133.675671643519" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="105" xr:uid="{76AFA6D3-C9B2-4488-8D85-5F096F9AC460}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:AC1048576" sheet="NUMERICAL DATA"/>
   </cacheSource>
@@ -10710,39 +11236,34 @@
   </cacheFields>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
-      <x14:pivotCacheDefinition pivotCacheId="1301859492"/>
-    </ext>
-  </extLst>
-</pivotCacheDefinition>
-</file>
-
-<file path=xl/pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Ananya Dwivedi" refreshedDate="46133.63565625" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="4" xr:uid="{A6D95273-D309-48CA-82BE-3129668C0243}">
-  <cacheSource type="worksheet">
-    <worksheetSource ref="A3:B7" sheet="PIVOT BY AGE, STIMULI"/>
-  </cacheSource>
-  <cacheFields count="2">
-    <cacheField name="Row Labels" numFmtId="0">
-      <sharedItems count="4">
-        <s v="ADS"/>
-        <s v="QUALITY"/>
-        <s v="VALUE"/>
-        <s v="Grand Total"/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="Average of SCORE" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0.64" maxValue="0.75"/>
-    </cacheField>
-  </cacheFields>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
-      <x14:pivotCacheDefinition/>
+      <x14:pivotCacheDefinition pivotCacheId="1540558722"/>
     </ext>
   </extLst>
 </pivotCacheDefinition>
 </file>
 
 <file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="4">
+  <r>
+    <x v="0"/>
+    <n v="0.75"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <n v="0.75"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <n v="0.64"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <n v="0.71333333333333337"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords2.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="105">
   <r>
     <x v="0"/>
@@ -14002,30 +14523,9 @@
 </pivotCacheRecords>
 </file>
 
-<file path=xl/pivotCache/pivotCacheRecords2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="4">
-  <r>
-    <x v="0"/>
-    <n v="0.75"/>
-  </r>
-  <r>
-    <x v="1"/>
-    <n v="0.75"/>
-  </r>
-  <r>
-    <x v="2"/>
-    <n v="0.64"/>
-  </r>
-  <r>
-    <x v="3"/>
-    <n v="0.71333333333333337"/>
-  </r>
-</pivotCacheRecords>
-</file>
-
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B15EEA91-50F9-4B67-8FC9-9F137747D2F8}" name="PivotTable4" cacheId="39" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="12">
-  <location ref="A27:B32" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8CCA83B2-9194-40C0-91D1-6E75B40CEB38}" name="PivotTable1" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="6">
+  <location ref="A3:B8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="29">
     <pivotField axis="axisRow" showAll="0">
       <items count="6">
@@ -14039,9 +14539,9 @@
     </pivotField>
     <pivotField showAll="0">
       <items count="4">
-        <item h="1" x="0"/>
+        <item x="0"/>
         <item x="1"/>
-        <item h="1" x="2"/>
+        <item x="2"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -14100,7 +14600,7 @@
     <dataField name="Average of CUTOMER LOYALTY(RESPONSE-R)" fld="28" subtotal="average" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="5">
-    <format dxfId="1">
+    <format dxfId="0">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="0" count="1">
@@ -14109,7 +14609,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="2">
+    <format dxfId="1">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="0" count="1">
@@ -14118,7 +14618,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="3">
+    <format dxfId="2">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="0" count="1">
@@ -14127,7 +14627,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="4">
+    <format dxfId="3">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="0" count="1">
@@ -14136,12 +14636,12 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="5">
+    <format dxfId="4">
       <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
-  <chartFormats count="2">
-    <chartFormat chart="6" format="0" series="1">
+  <chartFormats count="3">
+    <chartFormat chart="3" format="0" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -14150,7 +14650,16 @@
         </references>
       </pivotArea>
     </chartFormat>
-    <chartFormat chart="9" format="0" series="1">
+    <chartFormat chart="4" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="5" format="2" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -14173,7 +14682,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A83C55BB-F6F3-457C-B6BC-65BD16527A53}" name="PivotTable2" cacheId="38" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="9">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A83C55BB-F6F3-457C-B6BC-65BD16527A53}" name="PivotTable2" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="9">
   <location ref="A3:B7" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="2">
     <pivotField axis="axisRow" showAll="0">
@@ -14211,7 +14720,7 @@
     <dataField name="Sum of Average of SCORE2" fld="1" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="0">
+    <format dxfId="85">
       <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -14344,16 +14853,16 @@
 </file>
 
 <file path=xl/slicerCaches/slicerCache1.xml><?xml version="1.0" encoding="utf-8"?>
-<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_Gender" xr10:uid="{979819E0-7803-47E5-9144-E189105CE00C}" sourceName="Gender">
+<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_Gender" xr10:uid="{25A94799-4ACC-4344-9370-AD9DBBBFB02B}" sourceName="Gender">
   <pivotTables>
-    <pivotTable tabId="6" name="PivotTable4"/>
+    <pivotTable tabId="9" name="PivotTable1"/>
   </pivotTables>
   <data>
-    <tabular pivotCacheId="1301859492">
+    <tabular pivotCacheId="1540558722">
       <items count="3">
-        <i x="0"/>
+        <i x="0" s="1"/>
         <i x="1" s="1"/>
-        <i x="2" nd="1"/>
+        <i x="2" s="1" nd="1"/>
       </items>
     </tabular>
   </data>
@@ -14362,7 +14871,7 @@
 
 <file path=xl/slicers/slicer1.xml><?xml version="1.0" encoding="utf-8"?>
 <slicers xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10">
-  <slicer name="Gender" xr10:uid="{3F5AEC8B-D4FD-45D1-A258-22456598F714}" cache="Slicer_Gender" caption="Gender" rowHeight="234950"/>
+  <slicer name="Gender" xr10:uid="{E25D8EF3-8742-48BA-BDF5-70546CC22135}" cache="Slicer_Gender" caption="Gender" rowHeight="234950"/>
 </slicers>
 </file>
 
@@ -35000,12 +35509,12 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1F837DB-A010-42C7-B01C-123E06684FDD}">
-  <dimension ref="A3:B32"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{546FAFD5-1DF5-46C7-96F1-7669934502CE}">
+  <dimension ref="A3:B8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="39.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
@@ -35013,6 +35522,69 @@
         <v>145</v>
       </c>
       <c r="B3" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="25" t="s">
+        <v>37</v>
+      </c>
+      <c r="B4" s="26">
+        <v>3.0181818181818185</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" s="26">
+        <v>3.7253333333333321</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" s="25" t="s">
+        <v>63</v>
+      </c>
+      <c r="B6" s="26">
+        <v>3.4545454545454546</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" s="25" t="s">
+        <v>66</v>
+      </c>
+      <c r="B7" s="26">
+        <v>3.4571428571428577</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" s="25" t="s">
+        <v>146</v>
+      </c>
+      <c r="B8" s="26">
+        <v>3.6038461538461535</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1F837DB-A010-42C7-B01C-123E06684FDD}">
+  <dimension ref="A3:B7"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="39.77734375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="24" t="s">
+        <v>145</v>
+      </c>
+      <c r="B3" t="s">
         <v>150</v>
       </c>
     </row>
@@ -35020,7 +35592,7 @@
       <c r="A4" s="25" t="s">
         <v>144</v>
       </c>
-      <c r="B4" s="26">
+      <c r="B4">
         <v>0.75</v>
       </c>
     </row>
@@ -35028,7 +35600,7 @@
       <c r="A5" s="25" t="s">
         <v>143</v>
       </c>
-      <c r="B5" s="26">
+      <c r="B5">
         <v>0.75</v>
       </c>
     </row>
@@ -35036,7 +35608,7 @@
       <c r="A6" s="25" t="s">
         <v>142</v>
       </c>
-      <c r="B6" s="26">
+      <c r="B6">
         <v>0.64</v>
       </c>
     </row>
@@ -35044,65 +35616,17 @@
       <c r="A7" s="25" t="s">
         <v>146</v>
       </c>
-      <c r="B7" s="27">
+      <c r="B7" s="26">
         <v>2.14</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A27" s="24" t="s">
-        <v>145</v>
-      </c>
-      <c r="B27" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A28" s="25" t="s">
-        <v>37</v>
-      </c>
-      <c r="B28" s="27">
-        <v>2.75</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A29" s="25" t="s">
-        <v>26</v>
-      </c>
-      <c r="B29" s="27">
-        <v>3.6187500000000004</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A30" s="25" t="s">
-        <v>63</v>
-      </c>
-      <c r="B30" s="27">
-        <v>2.8</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A31" s="25" t="s">
-        <v>66</v>
-      </c>
-      <c r="B31" s="27">
-        <v>3.2666666666666662</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A32" s="25" t="s">
-        <v>146</v>
-      </c>
-      <c r="B32" s="27">
-        <v>3.3607843137254902</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId3"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D40581E-9F3A-454F-9127-68D0777A43CD}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
